--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -34307,12 +34307,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -34337,7 +34337,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -34346,81 +34346,100 @@
         </is>
       </c>
       <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
         <v>2</v>
       </c>
-      <c r="O202" t="n">
-        <v>2</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP202" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
-      <c r="AT202" t="n">
-        <v>0</v>
-      </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34447,17 +34466,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -34482,7 +34501,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -34496,21 +34515,98 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -34519,7 +34615,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -34527,9 +34623,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT203" t="n">
@@ -34537,47 +34638,47 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34604,17 +34705,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -34648,173 +34749,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
-      </c>
-      <c r="P204" t="n">
-        <v>0</v>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34846,12 +34855,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34876,7 +34885,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -34885,81 +34894,93 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34986,7 +35007,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -35021,7 +35042,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -35038,18 +35059,98 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -35143,17 +35244,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -35187,173 +35288,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
         <v>1</v>
       </c>
+      <c r="R207" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35385,12 +35394,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -35415,7 +35424,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -35429,6 +35438,9 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -35437,68 +35449,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35525,7 +35546,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -35560,7 +35581,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -35577,18 +35598,98 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -35682,17 +35783,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35731,168 +35832,76 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35924,12 +35933,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -35954,7 +35963,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -35963,81 +35972,93 @@
         </is>
       </c>
       <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
         <v>2</v>
       </c>
-      <c r="O211" t="n">
-        <v>2</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP211" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
-      <c r="AT211" t="n">
-        <v>0</v>
-      </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36064,7 +36085,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -36099,7 +36120,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -36116,18 +36137,98 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -36221,17 +36322,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -36265,173 +36366,81 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36463,12 +36472,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -36493,7 +36502,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -36502,81 +36511,93 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36603,17 +36624,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -36638,12 +36659,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -36652,76 +36673,168 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="R215" t="n">
-        <v>0</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36753,12 +36866,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -36783,22 +36896,22 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -36831,40 +36944,330 @@
       </c>
       <c r="AV216" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW216" t="inlineStr">
+      <c r="AW218" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX216" t="inlineStr">
+      <c r="AX218" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY216" t="inlineStr">
+      <c r="AY218" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ216" t="inlineStr">
+      <c r="AZ218" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA216" t="inlineStr">
+      <c r="BA218" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB216" t="inlineStr">
+      <c r="BB218" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC216" t="inlineStr">
+      <c r="BC218" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -36986,7 +37389,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -36996,7 +37399,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -37016,7 +37419,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -37011,12 +37011,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -37041,22 +37041,22 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -37089,42 +37089,42 @@
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37156,12 +37156,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -37234,40 +37234,185 @@
       </c>
       <c r="AV218" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW218" t="inlineStr">
+      <c r="AW219" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX218" t="inlineStr">
+      <c r="AX219" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY218" t="inlineStr">
+      <c r="AY219" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ218" t="inlineStr">
+      <c r="AZ219" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA218" t="inlineStr">
+      <c r="BA219" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB218" t="inlineStr">
+      <c r="BB219" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC218" t="inlineStr">
+      <c r="BC219" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -37389,7 +37534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -37399,7 +37544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
@@ -37451,7 +37596,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -37156,12 +37156,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -37186,12 +37186,12 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -37200,6 +37200,9 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -37208,68 +37211,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37296,125 +37308,652 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>D120</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
         <is>
           <t>破伤风</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N219" t="n">
-        <v>0</v>
-      </c>
-      <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="inlineStr">
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO219" t="inlineStr">
+      <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP219" t="inlineStr">
+      <c r="AP221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR219" t="inlineStr">
+      <c r="AR221" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS219" t="inlineStr"/>
-      <c r="AT219" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU219" t="inlineStr">
+      <c r="AS221" t="inlineStr"/>
+      <c r="AT221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU221" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV219" t="inlineStr">
+      <c r="AV221" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW219" t="inlineStr">
+      <c r="AW221" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX219" t="inlineStr">
+      <c r="AX221" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY219" t="inlineStr">
+      <c r="AY221" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ219" t="inlineStr">
+      <c r="AZ221" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA219" t="inlineStr">
+      <c r="BA221" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB219" t="inlineStr">
+      <c r="BB221" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC219" t="inlineStr">
+      <c r="BC221" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" t="n">
+        <v>2</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
+      <c r="AT222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37451,7 +37990,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -37534,7 +38073,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -37544,7 +38083,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
@@ -37564,7 +38103,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -37596,7 +38135,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -29162,12 +29162,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -29206,76 +29206,87 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29302,17 +29313,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -29346,81 +29357,170 @@
         </is>
       </c>
       <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary tetanus notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
         <v>1</v>
       </c>
-      <c r="O171" t="n">
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
         <v>1</v>
       </c>
-      <c r="R171" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP171" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
-      <c r="AT171" t="n">
-        <v>0</v>
-      </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29452,12 +29552,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29491,100 +29591,81 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29611,17 +29692,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29660,170 +29741,76 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>Stelkramp</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF173" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG173" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN173" t="b">
-        <v>1</v>
+      <c r="R173" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29855,12 +29842,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29885,7 +29872,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29894,81 +29881,100 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29995,17 +30001,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -30030,7 +30036,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -30044,76 +30050,170 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="R175" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -30145,12 +30245,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -30175,7 +30275,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -30189,9 +30289,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="P176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -30200,77 +30297,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30297,17 +30385,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30332,7 +30420,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -30341,173 +30429,81 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" t="n">
-        <v>0</v>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
         <v>1</v>
       </c>
+      <c r="R177" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30539,12 +30535,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30569,7 +30565,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -30578,81 +30574,93 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0.003267233630263065</v>
+        <v>0</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30679,17 +30687,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30714,7 +30722,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -30728,76 +30736,168 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="R179" t="n">
-        <v>0</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30829,12 +30929,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30859,7 +30959,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -30868,93 +30968,81 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30981,17 +31069,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -31016,7 +31104,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -31030,168 +31118,76 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31223,12 +31219,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -31253,7 +31249,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -31262,81 +31258,93 @@
         </is>
       </c>
       <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT182" t="n">
         <v>2</v>
       </c>
-      <c r="O182" t="n">
-        <v>2</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP182" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
-      <c r="AT182" t="n">
-        <v>0</v>
-      </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31363,17 +31371,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -31398,7 +31406,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -31412,76 +31420,168 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31513,12 +31613,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -31543,7 +31643,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -31552,93 +31652,81 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="P184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31665,17 +31753,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -31700,7 +31788,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -31714,168 +31802,76 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31907,12 +31903,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -31937,7 +31933,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -31946,81 +31942,93 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32047,17 +32055,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -32082,7 +32090,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -32096,76 +32104,168 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="R187" t="n">
-        <v>0</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32327,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -32236,13 +32336,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R188" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -32342,12 +32442,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -32372,7 +32472,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -32386,9 +32486,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -32397,77 +32494,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32494,17 +32582,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -32538,173 +32626,81 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O190" t="n">
-        <v>0</v>
-      </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32736,12 +32732,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -32766,12 +32762,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N191" t="n">
@@ -32780,6 +32776,9 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -32788,68 +32787,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32876,17 +32884,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32911,12 +32919,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N192" t="n">
@@ -32925,73 +32933,168 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33023,12 +33126,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -33067,9 +33170,12 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -33103,12 +33209,12 @@
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -33123,12 +33229,12 @@
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
@@ -33165,12 +33271,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -33245,7 +33351,7 @@
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
@@ -33265,7 +33371,7 @@
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
@@ -33307,12 +33413,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -33387,7 +33493,7 @@
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
@@ -33407,7 +33513,7 @@
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
@@ -33449,12 +33555,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -33529,7 +33635,7 @@
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
@@ -33549,7 +33655,7 @@
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
@@ -33591,12 +33697,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -33671,7 +33777,7 @@
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
@@ -33691,7 +33797,7 @@
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
@@ -33733,12 +33839,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -33813,7 +33919,7 @@
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
@@ -33833,7 +33939,7 @@
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
@@ -33875,12 +33981,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -33955,7 +34061,7 @@
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
@@ -33975,7 +34081,7 @@
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
@@ -34017,12 +34123,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -34056,17 +34162,14 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>9</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0.004214219717096481</v>
+        <v>0</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -34095,42 +34198,42 @@
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34162,12 +34265,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -34201,17 +34304,14 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>1</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -34240,42 +34340,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34307,12 +34407,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -34346,100 +34446,81 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O202" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>0.004214219717096481</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -34466,17 +34547,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -34510,175 +34591,81 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Stelkramp</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
         <v>1</v>
       </c>
+      <c r="R203" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34710,12 +34697,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -34740,7 +34727,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -34749,81 +34736,100 @@
         </is>
       </c>
       <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT204" t="n">
         <v>2</v>
       </c>
-      <c r="O204" t="n">
-        <v>2</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO204" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP204" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
-      <c r="AT204" t="n">
-        <v>0</v>
-      </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34850,17 +34856,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34885,7 +34891,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -34899,21 +34905,98 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="P205" t="n">
-        <v>0</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -34922,7 +35005,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -34930,9 +35013,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT205" t="n">
@@ -34940,47 +35028,47 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35007,17 +35095,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -35051,173 +35139,81 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35249,12 +35245,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -35279,7 +35275,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -35288,81 +35284,93 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35389,7 +35397,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -35424,7 +35432,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -35441,18 +35449,98 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -35546,17 +35634,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -35590,173 +35678,81 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
         <v>1</v>
       </c>
+      <c r="R209" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35788,12 +35784,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35818,7 +35814,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -35832,6 +35828,9 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -35840,68 +35839,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35928,7 +35936,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -35963,7 +35971,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -35980,18 +35988,98 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -36085,17 +36173,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -36134,168 +36222,76 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36327,12 +36323,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -36357,7 +36353,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -36366,81 +36362,93 @@
         </is>
       </c>
       <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
         <v>2</v>
       </c>
-      <c r="O213" t="n">
-        <v>2</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP213" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
-      <c r="AT213" t="n">
-        <v>0</v>
-      </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36467,7 +36475,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -36502,7 +36510,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -36519,18 +36527,98 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="R214" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -36624,17 +36712,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -36668,173 +36756,81 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O215" t="n">
-        <v>0</v>
-      </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36866,12 +36862,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -36896,7 +36892,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -36905,81 +36901,93 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37006,17 +37014,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -37041,7 +37049,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -37050,81 +37058,173 @@
         </is>
       </c>
       <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT217" t="n">
         <v>2</v>
       </c>
-      <c r="O217" t="n">
-        <v>2</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP217" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
-      <c r="AT217" t="n">
-        <v>0</v>
-      </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37156,12 +37256,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -37186,7 +37286,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -37195,93 +37295,81 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
-      </c>
-      <c r="P218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37308,17 +37396,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -37352,173 +37440,81 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="P219" t="n">
-        <v>0</v>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN219" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37550,12 +37546,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -37580,12 +37576,12 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -37594,6 +37590,9 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -37602,68 +37601,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37690,17 +37698,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -37725,12 +37733,12 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -37739,76 +37747,168 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37840,12 +37940,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -37870,7 +37970,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -37879,13 +37979,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -37918,40 +38018,330 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
+      <c r="AT223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>2</v>
+      </c>
+      <c r="O224" t="n">
+        <v>2</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW222" t="inlineStr">
+      <c r="AW224" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX222" t="inlineStr">
+      <c r="AX224" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY222" t="inlineStr">
+      <c r="AY224" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ222" t="inlineStr">
+      <c r="AZ224" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA222" t="inlineStr">
+      <c r="BA224" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB222" t="inlineStr">
+      <c r="BB224" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC222" t="inlineStr">
+      <c r="BC224" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -38073,7 +38463,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -38083,7 +38473,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -38103,7 +38493,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -38124,13 +38124,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -38344,6 +38344,151 @@
       <c r="BC224" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>5</v>
+      </c>
+      <c r="O225" t="n">
+        <v>5</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
+      <c r="AT225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38380,7 +38525,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -38463,7 +38608,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
@@ -38473,7 +38618,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -38525,7 +38670,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -29056,13 +29056,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="O169" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R169" t="n">
-        <v>0.03277726446630596</v>
+        <v>0.03745973081863539</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -34446,13 +34446,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="O202" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="R202" t="n">
-        <v>0.004214219717096481</v>
+        <v>0.01123791924559061</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>637</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -38492,6 +38492,400 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38608,7 +39002,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -38618,7 +39012,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -38638,7 +39032,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -29056,13 +29056,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O169" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R169" t="n">
-        <v>0.03745973081863539</v>
+        <v>0.03792797745386832</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -34446,13 +34446,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="O202" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="R202" t="n">
-        <v>0.01123791924559061</v>
+        <v>0.03418200437200478</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -34552,12 +34552,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -34591,13 +34591,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -34630,42 +34630,42 @@
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34697,12 +34697,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -34736,100 +34736,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34856,7 +34837,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -34905,98 +34886,23 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Stelkramp</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -35095,17 +35001,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -35130,7 +35036,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -35139,81 +35045,175 @@
         </is>
       </c>
       <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
         <v>2</v>
       </c>
-      <c r="O206" t="n">
-        <v>2</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP206" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
-      <c r="AT206" t="n">
-        <v>0</v>
-      </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35245,12 +35245,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -35284,93 +35284,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35397,7 +35385,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -35449,98 +35437,18 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -35634,17 +35542,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -35669,7 +35577,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -35678,81 +35586,173 @@
         </is>
       </c>
       <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
         <v>1</v>
       </c>
-      <c r="O209" t="n">
-        <v>1</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35784,12 +35784,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35823,93 +35823,81 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35936,7 +35924,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -35988,98 +35976,18 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN211" t="b">
-        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -36173,17 +36081,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -36208,7 +36116,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -36222,76 +36130,168 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36323,12 +36323,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -36367,9 +36367,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -36378,77 +36375,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36475,7 +36463,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -36527,98 +36515,18 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -36712,17 +36620,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -36747,7 +36655,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -36756,81 +36664,173 @@
         </is>
       </c>
       <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
         <v>2</v>
       </c>
-      <c r="O215" t="n">
-        <v>2</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP215" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
-      <c r="AT215" t="n">
-        <v>0</v>
-      </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36862,12 +36862,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -36901,93 +36901,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="P216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37014,7 +37002,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -37066,98 +37054,18 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -37251,17 +37159,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -37286,7 +37194,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -37295,81 +37203,173 @@
         </is>
       </c>
       <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
         <v>1</v>
       </c>
-      <c r="O218" t="n">
-        <v>1</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37401,12 +37401,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -37440,13 +37440,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R219" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -37479,42 +37479,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37546,12 +37546,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -37585,93 +37585,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37698,7 +37686,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -37750,98 +37738,18 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -37935,17 +37843,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -37970,12 +37878,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -37984,76 +37892,168 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38085,12 +38085,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -38124,13 +38124,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -38163,42 +38163,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38230,12 +38230,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -38260,7 +38260,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -38269,13 +38269,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R224" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.002341233176164712</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -38308,42 +38308,42 @@
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -38375,12 +38375,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -38414,13 +38414,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O225" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R225" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -38453,42 +38453,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38520,12 +38520,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -38559,93 +38559,81 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
-      </c>
-      <c r="P226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38672,215 +38660,1056 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>5</v>
+      </c>
+      <c r="O227" t="n">
+        <v>5</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
+      <c r="AT227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>D120</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
         <is>
           <t>破伤风</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="K229" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N227" t="n">
-        <v>0</v>
-      </c>
-      <c r="O227" t="n">
-        <v>0</v>
-      </c>
-      <c r="P227" t="n">
-        <v>0</v>
-      </c>
-      <c r="U227" t="inlineStr">
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="inlineStr">
         <is>
           <t>SER_SG_CDA_TETANUS</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
+      <c r="V229" t="inlineStr">
         <is>
           <t>SER_SG_CDA_TETANUS</t>
         </is>
       </c>
-      <c r="W227" t="inlineStr">
+      <c r="W229" t="inlineStr">
         <is>
           <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
+      <c r="Z229" t="inlineStr">
         <is>
           <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
-      <c r="AA227" t="inlineStr">
+      <c r="AA229" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB227" t="inlineStr">
+      <c r="AB229" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC227" t="inlineStr">
+      <c r="AC229" t="inlineStr">
         <is>
           <t>country:SG:national</t>
         </is>
       </c>
-      <c r="AD227" t="inlineStr">
+      <c r="AD229" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE227" t="inlineStr">
+      <c r="AE229" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF227" t="inlineStr">
+      <c r="AF229" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG227" t="inlineStr">
+      <c r="AG229" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH227" t="inlineStr">
+      <c r="AH229" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI227" t="inlineStr">
+      <c r="AI229" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ227" t="inlineStr">
+      <c r="AJ229" t="inlineStr">
         <is>
           <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
-      <c r="AK227" t="inlineStr">
+      <c r="AK229" t="inlineStr">
         <is>
           <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
-      <c r="AM227" t="inlineStr">
+      <c r="AM229" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN227" t="b">
+      <c r="AN229" t="b">
         <v>1</v>
       </c>
-      <c r="AO227" t="inlineStr">
+      <c r="AO229" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP227" t="inlineStr">
+      <c r="AP229" t="inlineStr">
         <is>
           <t>temporal_handoff</t>
         </is>
       </c>
-      <c r="AQ227" t="inlineStr">
+      <c r="AQ229" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS227" t="inlineStr">
+      <c r="AS229" t="inlineStr">
         <is>
           <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
         </is>
       </c>
-      <c r="AT227" t="n">
+      <c r="AT229" t="n">
         <v>2</v>
       </c>
-      <c r="AU227" t="inlineStr">
+      <c r="AU229" t="inlineStr">
         <is>
           <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
-      <c r="AV227" t="inlineStr">
+      <c r="AV229" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="AW227" t="inlineStr">
+      <c r="AW229" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="AX227" t="inlineStr">
+      <c r="AX229" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="AY227" t="inlineStr">
+      <c r="AY229" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
       </c>
-      <c r="AZ227" t="inlineStr">
+      <c r="AZ229" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="BA227" t="inlineStr">
+      <c r="BA229" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="BB227" t="inlineStr">
+      <c r="BB229" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="BC227" t="inlineStr">
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>3</v>
+      </c>
+      <c r="O230" t="n">
+        <v>3</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
+      <c r="AT230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -38919,7 +39748,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -39002,7 +39831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -39012,7 +39841,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -39032,7 +39861,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -39064,7 +39893,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>662</v>
+        <v>720</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -38414,13 +38414,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O225" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R225" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -39712,6 +39712,835 @@
       <c r="BC232" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" t="n">
+        <v>2</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="n">
+        <v>2</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
+      <c r="AT236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39748,7 +40577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -39831,7 +40660,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -39841,7 +40670,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -39861,7 +40690,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -39893,7 +40722,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -84282,6 +84282,151 @@
         </is>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N539" t="n">
+        <v>4</v>
+      </c>
+      <c r="O539" t="n">
+        <v>4</v>
+      </c>
+      <c r="R539" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO539" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP539" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR539" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS539" t="inlineStr"/>
+      <c r="AT539" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU539" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV539" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW539" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX539" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY539" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA539" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB539" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC539" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -84315,7 +84460,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -84398,7 +84543,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10">
@@ -84408,7 +84553,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11">
@@ -84460,7 +84605,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1410</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -8543,9 +8543,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -18424,9 +18421,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -26914,9 +26908,6 @@
       </c>
       <c r="O171" t="n">
         <v>1</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0.0002865038132769385</v>
